--- a/tests/fixtures/nisa/NISA_Monthly_Exposure_Summary_sanitized.xlsx
+++ b/tests/fixtures/nisa/NISA_Monthly_Exposure_Summary_sanitized.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exposure Maturity Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exposure Maturity Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,207 +416,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A2:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Counterparty</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Product Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Current Exposure</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Years to Maturity</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Maturity Date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alpha Clearing</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Interest Rate Swap</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0-1Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bravo Bank</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Return Swaps</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>320000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2027-12-31</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1-3Y</t>
+          <t>EXPOSURE MATURITY SCHEDULE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
-          <t>Canyon Capital</t>
+          <t>Px Date</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="H4" s="1" t="n">
+        <v>46053</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
         <is>
-          <t>Repo</t>
+          <t>NISA TIPS</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>Reverse Repo</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
-          <t>0-1Y</t>
+          <t>Total Return Swaps</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F14" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="F15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
-          <t>Delta Prime</t>
+          <t>Total</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FX Forward</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>640000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2029-06-30</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3-5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Echo Markets</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Commodity Swap</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>410000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2030-12-31</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>5Y+</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Foxtrot House</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Return Swaps</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2030-01-31</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3-5Y</t>
-        </is>
+      <c r="F16" t="n">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -622,38 +491,263 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>sanitized</t>
-        </is>
-      </c>
-      <c r="B1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative values only; no production counterparties.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C65FCF9450CF274D895D217D06427C63" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4f18e3f688999b7982922ca1d5df86c9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43c61a4d-e280-448f-ac33-458af3491a96" xmlns:ns3="572a816a-d0e5-4d5f-af6c-607c21ce9730" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ffca47ab87c523ca8807fb4c517d03d" ns2:_="" ns3:_="">
+    <xsd:import namespace="43c61a4d-e280-448f-ac33-458af3491a96"/>
+    <xsd:import namespace="572a816a-d0e5-4d5f-af6c-607c21ce9730"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="43c61a4d-e280-448f-ac33-458af3491a96" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a2a9e45-8854-4766-8f58-1e4aac2d4691" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="572a816a-d0e5-4d5f-af6c-607c21ce9730" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{7fac1087-e5e7-45cd-839f-c8b7169bad38}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="572a816a-d0e5-4d5f-af6c-607c21ce9730">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="572a816a-d0e5-4d5f-af6c-607c21ce9730" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43c61a4d-e280-448f-ac33-458af3491a96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5692EA3F-0AB2-4C6E-82AF-D06F71A871AD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AD85D1A-6FB9-4FA9-BC77-26E3A91E8CDF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D68CF35-70FD-415C-8159-4E3F416A576A}"/>
 </file>